--- a/project/excel/translator_testing_model.xlsx
+++ b/project/excel/translator_testing_model.xlsx
@@ -1945,7 +1945,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>output_id</t>
+          <t>output_ids</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>output_id</t>
+          <t>output_ids</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>output_id</t>
+          <t>output_ids</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">

--- a/project/excel/translator_testing_model.xlsx
+++ b/project/excel/translator_testing_model.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S1"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,37 +534,32 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>test_env</t>
+          <t>id</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>name</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>description</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>tags</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
         <is>
           <t>test_runner_settings</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="6">
+  <dataValidations count="5">
     <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"treats"</formula1>
     </dataValidation>
@@ -579,9 +574,6 @@
     </dataValidation>
     <dataValidation sqref="M2:M1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ars,arax,explanatory,improving,aragorn,bte,unsecret,rtxkg2,icees,cam,spoke,molepro,genetics,textmining,cohd,openpredict,collaboratory,connections"</formula1>
-    </dataValidation>
-    <dataValidation sqref="N2:N1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"dev,ci,test,prod"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -594,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -615,45 +607,37 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>test_env</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>name</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>tags</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
         <is>
           <t>test_runner_settings</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="2">
     <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"AcceptanceTest,BenchmarkTest,QuantitativeTest,StandardsValidationTest,OneHopTest"</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ars,arax,explanatory,improving,aragorn,bte,unsecret,rtxkg2,icees,cam,spoke,molepro,genetics,textmining,cohd,openpredict,collaboratory,connections"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D2:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"dev,ci,test,prod"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -666,7 +650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S1"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -737,37 +721,32 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>test_env</t>
+          <t>id</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>name</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>description</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>tags</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
         <is>
           <t>test_runner_settings</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="6">
+  <dataValidations count="5">
     <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"treats"</formula1>
     </dataValidation>
@@ -782,9 +761,6 @@
     </dataValidation>
     <dataValidation sqref="M2:M1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ars,arax,explanatory,improving,aragorn,bte,unsecret,rtxkg2,icees,cam,spoke,molepro,genetics,textmining,cohd,openpredict,collaboratory,connections"</formula1>
-    </dataValidation>
-    <dataValidation sqref="N2:N1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"dev,ci,test,prod"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -797,7 +773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S1"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -868,37 +844,32 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>test_env</t>
+          <t>id</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>name</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>description</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>tags</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
         <is>
           <t>test_runner_settings</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="6">
+  <dataValidations count="5">
     <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"treats"</formula1>
     </dataValidation>
@@ -913,9 +884,6 @@
     </dataValidation>
     <dataValidation sqref="M2:M1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ars,arax,explanatory,improving,aragorn,bte,unsecret,rtxkg2,icees,cam,spoke,molepro,genetics,textmining,cohd,openpredict,collaboratory,connections"</formula1>
-    </dataValidation>
-    <dataValidation sqref="N2:N1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"dev,ci,test,prod"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -928,7 +896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U1"/>
+  <dimension ref="A1:T1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1009,37 +977,32 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>test_env</t>
+          <t>id</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>name</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>description</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>tags</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
         <is>
           <t>test_runner_settings</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="6">
+  <dataValidations count="5">
     <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"treats"</formula1>
     </dataValidation>
@@ -1054,9 +1017,6 @@
     </dataValidation>
     <dataValidation sqref="O2:O1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ars,arax,explanatory,improving,aragorn,bte,unsecret,rtxkg2,icees,cam,spoke,molepro,genetics,textmining,cohd,openpredict,collaboratory,connections"</formula1>
-    </dataValidation>
-    <dataValidation sqref="P2:P1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"dev,ci,test,prod"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/project/excel/translator_testing_model.xlsx
+++ b/project/excel/translator_testing_model.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:T1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,25 +534,35 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>skip</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>skip_reason</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>id</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>test_runner_settings</t>
         </is>
@@ -586,7 +596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -607,25 +617,35 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>skip</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>skip_reason</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>id</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>test_runner_settings</t>
         </is>
@@ -645,252 +665,6 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:R1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>query_type</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>test_assets</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>preconditions</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>trapi_template</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>test_case_objective</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>test_case_source</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>test_case_predicate_name</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>test_case_predicate_id</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>test_case_input_id</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>qualifiers</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>input_category</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>output_category</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>components</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>test_runner_settings</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="5">
-    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"treats"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D2:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"ameliorates,treats,three_hop,drug_treats_rare_disease,drug-to-gene"</formula1>
-    </dataValidation>
-    <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"AcceptanceTest,BenchmarkTest,QuantitativeTest,StandardsValidationTest,OneHopTest"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F2:F1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"SME,SMURF,GitHubUserFeedback,TACT,BenchMark,TranslatorTeam,TestDataLocation"</formula1>
-    </dataValidation>
-    <dataValidation sqref="M2:M1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"ars,arax,explanatory,improving,aragorn,bte,unsecret,rtxkg2,icees,cam,spoke,molepro,genetics,textmining,cohd,openpredict,collaboratory,connections"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:R1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>query_type</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>test_assets</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>preconditions</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>trapi_template</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>test_case_objective</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>test_case_source</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>test_case_predicate_name</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>test_case_predicate_id</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>test_case_input_id</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>qualifiers</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>input_category</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>output_category</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>components</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>test_runner_settings</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="5">
-    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"treats"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D2:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"ameliorates,treats,three_hop,drug_treats_rare_disease,drug-to-gene"</formula1>
-    </dataValidation>
-    <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"AcceptanceTest,BenchmarkTest,QuantitativeTest,StandardsValidationTest,OneHopTest"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F2:F1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"SME,SMURF,GitHubUserFeedback,TACT,BenchMark,TranslatorTeam,TestDataLocation"</formula1>
-    </dataValidation>
-    <dataValidation sqref="M2:M1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"ars,arax,explanatory,improving,aragorn,bte,unsecret,rtxkg2,icees,cam,spoke,molepro,genetics,textmining,cohd,openpredict,collaboratory,connections"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -902,6 +676,272 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>query_type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>test_assets</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>preconditions</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>trapi_template</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>test_case_objective</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>test_case_source</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>test_case_predicate_name</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>test_case_predicate_id</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>test_case_input_id</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>qualifiers</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>input_category</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>output_category</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>components</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>skip</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>skip_reason</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>test_runner_settings</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="5">
+    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"treats"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"ameliorates,treats,three_hop,drug_treats_rare_disease,drug-to-gene"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"AcceptanceTest,BenchmarkTest,QuantitativeTest,StandardsValidationTest,OneHopTest"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"SME,SMURF,GitHubUserFeedback,TACT,BenchMark,TranslatorTeam,TestDataLocation"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M2:M1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"ars,arax,explanatory,improving,aragorn,bte,unsecret,rtxkg2,icees,cam,spoke,molepro,genetics,textmining,cohd,openpredict,collaboratory,connections"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>query_type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>test_assets</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>preconditions</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>trapi_template</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>test_case_objective</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>test_case_source</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>test_case_predicate_name</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>test_case_predicate_id</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>test_case_input_id</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>qualifiers</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>input_category</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>output_category</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>components</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>skip</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>skip_reason</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>test_runner_settings</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="5">
+    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"treats"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"ameliorates,treats,three_hop,drug_treats_rare_disease,drug-to-gene"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"AcceptanceTest,BenchmarkTest,QuantitativeTest,StandardsValidationTest,OneHopTest"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"SME,SMURF,GitHubUserFeedback,TACT,BenchMark,TranslatorTeam,TestDataLocation"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M2:M1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"ars,arax,explanatory,improving,aragorn,bte,unsecret,rtxkg2,icees,cam,spoke,molepro,genetics,textmining,cohd,openpredict,collaboratory,connections"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
           <t>test_run_time</t>
         </is>
       </c>
@@ -977,25 +1017,35 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>skip</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>skip_reason</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
           <t>id</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>test_runner_settings</t>
         </is>
@@ -1874,7 +1924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V1"/>
+  <dimension ref="A1:X1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1965,25 +2015,35 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
+          <t>skip</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>skip_reason</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
           <t>id</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>test_runner_settings</t>
         </is>
@@ -2008,7 +2068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:S1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2074,25 +2134,35 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>skip</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>skip_reason</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>id</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>test_runner_settings</t>
         </is>
@@ -2109,7 +2179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AH1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2250,25 +2320,35 @@
       </c>
       <c r="AB1" t="inlineStr">
         <is>
+          <t>skip</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>skip_reason</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>test_runner_settings</t>
         </is>
@@ -2305,7 +2385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V1"/>
+  <dimension ref="A1:X1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2396,25 +2476,35 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
+          <t>skip</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>skip_reason</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
           <t>id</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>test_runner_settings</t>
         </is>
